--- a/Gravedigger2026/Assets/ConfigTables/Mode2/Excel/关卡_子关卡表_Level_SubLevelConfig.xlsx
+++ b/Gravedigger2026/Assets/ConfigTables/Mode2/Excel/关卡_子关卡表_Level_SubLevelConfig.xlsx
@@ -32,7 +32,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="516" uniqueCount="141">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="518" uniqueCount="143">
   <si>
     <t>玩法选项ID</t>
   </si>
@@ -298,6 +298,9 @@
     <t>L01_S9_Dig_1</t>
   </si>
   <si>
+    <t>SearchExtract_02</t>
+  </si>
+  <si>
     <t>L01_S9_Dig_2</t>
   </si>
   <si>
@@ -380,6 +383,9 @@
   </si>
   <si>
     <t>L02_S9_Dig_1</t>
+  </si>
+  <si>
+    <t>SearchExtract_03</t>
   </si>
   <si>
     <t>L02_S9_Dig_2</t>
@@ -1469,7 +1475,7 @@
   <cols>
     <col min="1" max="1" width="18.125" customWidth="1"/>
     <col min="2" max="2" width="17.125" customWidth="1"/>
-    <col min="3" max="3" width="12.875" customWidth="1"/>
+    <col min="3" max="3" width="18.5" customWidth="1"/>
     <col min="4" max="4" width="9" style="2" customWidth="1"/>
     <col min="5" max="5" width="23.5" customWidth="1"/>
     <col min="6" max="6" width="19.125" customWidth="1"/>
@@ -1574,10 +1580,10 @@
       <c r="F3" s="1" t="s">
         <v>29</v>
       </c>
-      <c r="G3" t="s">
+      <c r="G3" s="1" t="s">
         <v>30</v>
       </c>
-      <c r="H3" t="s">
+      <c r="H3" s="1" t="s">
         <v>31</v>
       </c>
       <c r="I3" s="1" t="s">
@@ -1980,7 +1986,7 @@
         <v>60</v>
       </c>
       <c r="C18" t="s">
-        <v>61</v>
+        <v>88</v>
       </c>
       <c r="D18" s="2">
         <v>2</v>
@@ -2007,7 +2013,7 @@
         <v>67</v>
       </c>
       <c r="L18" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
     </row>
     <row r="19" spans="1:18">
@@ -2033,12 +2039,12 @@
         <v>43</v>
       </c>
       <c r="L19" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
     </row>
     <row r="20" spans="1:18">
       <c r="A20" s="4" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="B20" t="s">
         <v>37</v>
@@ -2059,12 +2065,12 @@
         <v>43</v>
       </c>
       <c r="L20" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
     </row>
     <row r="21" spans="1:18">
       <c r="A21" s="4" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="B21" t="s">
         <v>54</v>
@@ -2085,41 +2091,44 @@
         <v>58</v>
       </c>
       <c r="L21" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
     </row>
     <row r="22" spans="1:18">
       <c r="A22" s="4" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="B22" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="C22" s="5" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="F22" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="G22" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="H22" t="s">
         <v>40</v>
       </c>
       <c r="I22" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="J22" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="K22" t="s">
         <v>67</v>
       </c>
+      <c r="L22" t="s">
+        <v>98</v>
+      </c>
     </row>
     <row r="23" spans="1:18">
       <c r="A23" s="6" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="B23" t="s">
         <v>37</v>
@@ -2143,12 +2152,12 @@
         <v>43</v>
       </c>
       <c r="L23" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
     </row>
     <row r="24" spans="1:18">
       <c r="A24" s="6" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="B24" t="s">
         <v>37</v>
@@ -2169,12 +2178,12 @@
         <v>43</v>
       </c>
       <c r="L24" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
     </row>
     <row r="25" spans="1:18">
       <c r="A25" s="6" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="B25" t="s">
         <v>37</v>
@@ -2195,12 +2204,12 @@
         <v>53</v>
       </c>
       <c r="L25" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
     </row>
     <row r="26" spans="1:18">
       <c r="A26" s="6" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="B26" t="s">
         <v>54</v>
@@ -2221,18 +2230,18 @@
         <v>58</v>
       </c>
       <c r="L26" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
     </row>
     <row r="27" spans="1:18">
       <c r="A27" s="6" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="B27" t="s">
         <v>60</v>
       </c>
       <c r="C27" t="s">
-        <v>61</v>
+        <v>88</v>
       </c>
       <c r="D27" s="2">
         <v>1</v>
@@ -2259,12 +2268,12 @@
         <v>67</v>
       </c>
       <c r="L27" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
     </row>
     <row r="28" spans="1:18">
       <c r="A28" s="6" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="B28" t="s">
         <v>37</v>
@@ -2285,12 +2294,12 @@
         <v>43</v>
       </c>
       <c r="L28" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
     </row>
     <row r="29" spans="1:18">
       <c r="A29" s="6" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="B29" t="s">
         <v>37</v>
@@ -2311,12 +2320,12 @@
         <v>53</v>
       </c>
       <c r="L29" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
     </row>
     <row r="30" spans="1:18">
       <c r="A30" s="6" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="B30" t="s">
         <v>76</v>
@@ -2337,12 +2346,12 @@
         <v>80</v>
       </c>
       <c r="L30" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
     </row>
     <row r="31" spans="1:18">
       <c r="A31" s="6" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="B31" t="s">
         <v>37</v>
@@ -2363,12 +2372,12 @@
         <v>43</v>
       </c>
       <c r="L31" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
     </row>
     <row r="32" spans="1:18">
       <c r="A32" s="6" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="B32" t="s">
         <v>37</v>
@@ -2389,14 +2398,14 @@
         <v>43</v>
       </c>
       <c r="L32" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="Q32" s="7"/>
       <c r="R32" s="7"/>
     </row>
     <row r="33" spans="1:18">
       <c r="A33" s="6" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="B33" t="s">
         <v>37</v>
@@ -2417,14 +2426,14 @@
         <v>43</v>
       </c>
       <c r="L33" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="Q33" s="7"/>
       <c r="R33" s="7"/>
     </row>
     <row r="34" spans="1:18">
       <c r="A34" s="6" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="B34" t="s">
         <v>54</v>
@@ -2445,14 +2454,14 @@
         <v>58</v>
       </c>
       <c r="L34" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="Q34" s="7"/>
       <c r="R34" s="7"/>
     </row>
     <row r="35" spans="1:18">
       <c r="A35" s="6" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="B35" t="s">
         <v>54</v>
@@ -2473,14 +2482,14 @@
         <v>58</v>
       </c>
       <c r="L35" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="Q35" s="7"/>
       <c r="R35" s="7"/>
     </row>
     <row r="36" spans="1:18">
       <c r="A36" s="6" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="B36" t="s">
         <v>76</v>
@@ -2501,20 +2510,20 @@
         <v>80</v>
       </c>
       <c r="L36" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="Q36" s="7"/>
       <c r="R36" s="7"/>
     </row>
     <row r="37" spans="1:18">
       <c r="A37" s="6" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="B37" t="s">
         <v>60</v>
       </c>
       <c r="C37" t="s">
-        <v>61</v>
+        <v>117</v>
       </c>
       <c r="D37" s="2">
         <v>2</v>
@@ -2541,14 +2550,14 @@
         <v>67</v>
       </c>
       <c r="L37" t="s">
-        <v>116</v>
+        <v>118</v>
       </c>
       <c r="Q37" s="7"/>
       <c r="R37" s="7"/>
     </row>
     <row r="38" spans="1:18">
       <c r="A38" s="6" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="B38" t="s">
         <v>37</v>
@@ -2569,14 +2578,14 @@
         <v>43</v>
       </c>
       <c r="L38" t="s">
-        <v>117</v>
+        <v>119</v>
       </c>
       <c r="Q38" s="7"/>
       <c r="R38" s="7"/>
     </row>
     <row r="39" spans="1:18">
       <c r="A39" s="6" t="s">
-        <v>116</v>
+        <v>118</v>
       </c>
       <c r="B39" t="s">
         <v>37</v>
@@ -2597,14 +2606,14 @@
         <v>43</v>
       </c>
       <c r="L39" t="s">
-        <v>117</v>
+        <v>119</v>
       </c>
       <c r="Q39" s="7"/>
       <c r="R39" s="7"/>
     </row>
     <row r="40" spans="1:18">
       <c r="A40" s="6" t="s">
-        <v>117</v>
+        <v>119</v>
       </c>
       <c r="B40" t="s">
         <v>54</v>
@@ -2625,45 +2634,48 @@
         <v>58</v>
       </c>
       <c r="L40" t="s">
-        <v>118</v>
+        <v>120</v>
       </c>
       <c r="Q40" s="7"/>
       <c r="R40" s="7"/>
     </row>
     <row r="41" spans="1:18">
       <c r="A41" s="6" t="s">
-        <v>118</v>
+        <v>120</v>
       </c>
       <c r="B41" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="C41" s="5" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="F41" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="G41" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="H41" t="s">
         <v>40</v>
       </c>
       <c r="I41" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="J41" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="K41" t="s">
         <v>67</v>
       </c>
+      <c r="L41" t="s">
+        <v>121</v>
+      </c>
       <c r="Q41" s="7"/>
       <c r="R41" s="7"/>
     </row>
     <row r="42" spans="1:18">
       <c r="A42" s="8" t="s">
-        <v>119</v>
+        <v>121</v>
       </c>
       <c r="B42" t="s">
         <v>37</v>
@@ -2687,13 +2699,13 @@
         <v>43</v>
       </c>
       <c r="L42" t="s">
-        <v>120</v>
+        <v>122</v>
       </c>
       <c r="R42" s="7"/>
     </row>
     <row r="43" spans="1:18">
       <c r="A43" s="8" t="s">
-        <v>121</v>
+        <v>123</v>
       </c>
       <c r="B43" t="s">
         <v>37</v>
@@ -2714,13 +2726,13 @@
         <v>43</v>
       </c>
       <c r="L43" t="s">
-        <v>122</v>
+        <v>124</v>
       </c>
       <c r="R43" s="7"/>
     </row>
     <row r="44" spans="1:18">
       <c r="A44" s="8" t="s">
-        <v>123</v>
+        <v>125</v>
       </c>
       <c r="B44" t="s">
         <v>37</v>
@@ -2741,13 +2753,13 @@
         <v>53</v>
       </c>
       <c r="L44" t="s">
-        <v>122</v>
+        <v>124</v>
       </c>
       <c r="R44" s="7"/>
     </row>
     <row r="45" spans="1:18">
       <c r="A45" s="8" t="s">
-        <v>122</v>
+        <v>124</v>
       </c>
       <c r="B45" t="s">
         <v>54</v>
@@ -2768,19 +2780,19 @@
         <v>58</v>
       </c>
       <c r="L45" t="s">
-        <v>124</v>
+        <v>126</v>
       </c>
       <c r="R45" s="7"/>
     </row>
     <row r="46" spans="1:18">
       <c r="A46" s="8" t="s">
-        <v>124</v>
+        <v>126</v>
       </c>
       <c r="B46" t="s">
         <v>60</v>
       </c>
       <c r="C46" t="s">
-        <v>61</v>
+        <v>88</v>
       </c>
       <c r="D46" s="2">
         <v>1</v>
@@ -2807,13 +2819,13 @@
         <v>67</v>
       </c>
       <c r="L46" t="s">
-        <v>125</v>
+        <v>127</v>
       </c>
       <c r="R46" s="7"/>
     </row>
     <row r="47" spans="1:18">
       <c r="A47" s="8" t="s">
-        <v>126</v>
+        <v>128</v>
       </c>
       <c r="B47" t="s">
         <v>37</v>
@@ -2834,13 +2846,13 @@
         <v>43</v>
       </c>
       <c r="L47" t="s">
-        <v>127</v>
+        <v>129</v>
       </c>
       <c r="R47" s="7"/>
     </row>
     <row r="48" spans="1:18">
       <c r="A48" s="8" t="s">
-        <v>128</v>
+        <v>130</v>
       </c>
       <c r="B48" t="s">
         <v>37</v>
@@ -2861,13 +2873,13 @@
         <v>53</v>
       </c>
       <c r="L48" t="s">
-        <v>129</v>
+        <v>131</v>
       </c>
       <c r="R48" s="7"/>
     </row>
     <row r="49" spans="1:18">
       <c r="A49" s="8" t="s">
-        <v>130</v>
+        <v>132</v>
       </c>
       <c r="B49" t="s">
         <v>76</v>
@@ -2888,13 +2900,13 @@
         <v>80</v>
       </c>
       <c r="L49" t="s">
-        <v>131</v>
+        <v>133</v>
       </c>
       <c r="R49" s="7"/>
     </row>
     <row r="50" spans="1:18">
       <c r="A50" s="8" t="s">
-        <v>127</v>
+        <v>129</v>
       </c>
       <c r="B50" t="s">
         <v>37</v>
@@ -2915,13 +2927,13 @@
         <v>43</v>
       </c>
       <c r="L50" t="s">
-        <v>132</v>
+        <v>134</v>
       </c>
       <c r="R50" s="7"/>
     </row>
     <row r="51" spans="1:18">
       <c r="A51" s="8" t="s">
-        <v>129</v>
+        <v>131</v>
       </c>
       <c r="B51" t="s">
         <v>37</v>
@@ -2942,14 +2954,14 @@
         <v>43</v>
       </c>
       <c r="L51" t="s">
-        <v>133</v>
+        <v>135</v>
       </c>
       <c r="Q51" s="7"/>
       <c r="R51" s="7"/>
     </row>
     <row r="52" spans="1:18">
       <c r="A52" s="8" t="s">
-        <v>131</v>
+        <v>133</v>
       </c>
       <c r="B52" t="s">
         <v>37</v>
@@ -2970,14 +2982,14 @@
         <v>43</v>
       </c>
       <c r="L52" t="s">
-        <v>134</v>
+        <v>136</v>
       </c>
       <c r="Q52" s="7"/>
       <c r="R52" s="7"/>
     </row>
     <row r="53" spans="1:18">
       <c r="A53" s="8" t="s">
-        <v>132</v>
+        <v>134</v>
       </c>
       <c r="B53" t="s">
         <v>54</v>
@@ -2998,14 +3010,14 @@
         <v>58</v>
       </c>
       <c r="L53" t="s">
-        <v>135</v>
+        <v>137</v>
       </c>
       <c r="Q53" s="7"/>
       <c r="R53" s="7"/>
     </row>
     <row r="54" spans="1:18">
       <c r="A54" s="8" t="s">
-        <v>134</v>
+        <v>136</v>
       </c>
       <c r="B54" t="s">
         <v>54</v>
@@ -3026,14 +3038,14 @@
         <v>58</v>
       </c>
       <c r="L54" t="s">
-        <v>136</v>
+        <v>138</v>
       </c>
       <c r="Q54" s="7"/>
       <c r="R54" s="7"/>
     </row>
     <row r="55" spans="1:18">
       <c r="A55" s="8" t="s">
-        <v>135</v>
+        <v>137</v>
       </c>
       <c r="B55" t="s">
         <v>76</v>
@@ -3054,20 +3066,20 @@
         <v>80</v>
       </c>
       <c r="L55" t="s">
-        <v>137</v>
+        <v>139</v>
       </c>
       <c r="Q55" s="7"/>
       <c r="R55" s="7"/>
     </row>
     <row r="56" spans="1:18">
       <c r="A56" s="8" t="s">
-        <v>136</v>
+        <v>138</v>
       </c>
       <c r="B56" t="s">
         <v>60</v>
       </c>
       <c r="C56" t="s">
-        <v>61</v>
+        <v>117</v>
       </c>
       <c r="D56" s="2">
         <v>2</v>
@@ -3094,14 +3106,14 @@
         <v>67</v>
       </c>
       <c r="L56" t="s">
-        <v>138</v>
+        <v>140</v>
       </c>
       <c r="Q56" s="7"/>
       <c r="R56" s="7"/>
     </row>
     <row r="57" spans="1:18">
       <c r="A57" s="8" t="s">
-        <v>137</v>
+        <v>139</v>
       </c>
       <c r="B57" t="s">
         <v>37</v>
@@ -3122,14 +3134,14 @@
         <v>43</v>
       </c>
       <c r="L57" t="s">
-        <v>139</v>
+        <v>141</v>
       </c>
       <c r="Q57" s="7"/>
       <c r="R57" s="7"/>
     </row>
     <row r="58" spans="1:18">
       <c r="A58" s="8" t="s">
-        <v>138</v>
+        <v>140</v>
       </c>
       <c r="B58" t="s">
         <v>37</v>
@@ -3150,14 +3162,14 @@
         <v>43</v>
       </c>
       <c r="L58" t="s">
-        <v>139</v>
+        <v>141</v>
       </c>
       <c r="Q58" s="7"/>
       <c r="R58" s="7"/>
     </row>
     <row r="59" spans="1:18">
       <c r="A59" s="8" t="s">
-        <v>139</v>
+        <v>141</v>
       </c>
       <c r="B59" t="s">
         <v>54</v>
@@ -3178,35 +3190,35 @@
         <v>58</v>
       </c>
       <c r="L59" t="s">
-        <v>140</v>
+        <v>142</v>
       </c>
       <c r="Q59" s="7"/>
       <c r="R59" s="7"/>
     </row>
     <row r="60" spans="1:18">
       <c r="A60" s="8" t="s">
-        <v>140</v>
+        <v>142</v>
       </c>
       <c r="B60" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="C60" s="5" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="F60" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="G60" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="H60" t="s">
         <v>40</v>
       </c>
       <c r="I60" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="J60" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="K60" t="s">
         <v>67</v>
